--- a/human_resources_forms/005_pharmaceutical_industry_employment_form--human_resources_forms.xlsx
+++ b/human_resources_forms/005_pharmaceutical_industry_employment_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sales_representative'}</t>
+          <t>sales_representative</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sales Representative'}</t>
+          <t>Sales Representative</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing_manager'}</t>
+          <t>marketing_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Marketing Manager'}</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'operations_manager'}</t>
+          <t>operations_manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Operations Manager'}</t>
+          <t>Operations Manager</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new_york_city'}</t>
+          <t>new_york_city</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New York City'}</t>
+          <t>New York City</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chicago'}</t>
+          <t>chicago</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Chicago'}</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'los_angeles'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Los Angeles'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-Time'}</t>
+          <t>Full-Time</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-Time'}</t>
+          <t>Part-Time</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'passive'}</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Passive'}</t>
+          <t>Passive</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'permanent'}</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Permanent'}</t>
+          <t>Permanent</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
